--- a/result/morris/morris_first_inf_ONLY_MAE_N512_seed2024.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N512_seed2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,129 +453,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.99039713541667</v>
+        <v>-4.924641927083336</v>
       </c>
       <c r="C2" t="n">
-        <v>17.10422092013889</v>
+        <v>15.75840928819444</v>
       </c>
       <c r="D2" t="n">
-        <v>22.0925934822397</v>
+        <v>27.33726972650521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.47829861111111</v>
+        <v>1.484863281250001</v>
       </c>
       <c r="C3" t="n">
-        <v>17.06358506944446</v>
+        <v>14.6940646701389</v>
       </c>
       <c r="D3" t="n">
-        <v>24.20248204871763</v>
+        <v>26.04785473240808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-7.928982204861114</v>
+        <v>4.134982638888889</v>
       </c>
       <c r="C4" t="n">
-        <v>16.24256727430554</v>
+        <v>11.88151041666665</v>
       </c>
       <c r="D4" t="n">
-        <v>26.57766311883395</v>
+        <v>17.47606235979871</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.02023654513889</v>
+        <v>1.71923828125</v>
       </c>
       <c r="C5" t="n">
-        <v>15.89425998263888</v>
+        <v>11.86235894097222</v>
       </c>
       <c r="D5" t="n">
-        <v>25.18005619487446</v>
+        <v>18.56173342389327</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.06559244791666663</v>
+        <v>0.8804253472222218</v>
       </c>
       <c r="C6" t="n">
-        <v>6.141655815972221</v>
+        <v>8.310763888888896</v>
       </c>
       <c r="D6" t="n">
-        <v>14.09968187010757</v>
+        <v>14.8438035640204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.299858940972223</v>
+        <v>0.9837239583333337</v>
       </c>
       <c r="C7" t="n">
-        <v>3.455457899305558</v>
+        <v>7.954861111111114</v>
       </c>
       <c r="D7" t="n">
-        <v>7.898569059871815</v>
+        <v>15.20675083774748</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4521484375</v>
+        <v>-0.3549804687500007</v>
       </c>
       <c r="C8" t="n">
-        <v>2.556857638888889</v>
+        <v>4.734429253472223</v>
       </c>
       <c r="D8" t="n">
-        <v>8.614574580818287</v>
+        <v>12.04182067279304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.626356336805556</v>
+        <v>2.505154079861112</v>
       </c>
       <c r="C9" t="n">
-        <v>2.003092447916667</v>
+        <v>4.364854600694446</v>
       </c>
       <c r="D9" t="n">
-        <v>7.33753787382845</v>
+        <v>12.1173446186958</v>
       </c>
     </row>
     <row r="10">
@@ -585,61 +585,77 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5913628472222221</v>
+        <v>-0.2426757812500002</v>
       </c>
       <c r="C10" t="n">
-        <v>1.787109375</v>
+        <v>2.653157552083334</v>
       </c>
       <c r="D10" t="n">
-        <v>10.55492877159912</v>
+        <v>7.886156786702414</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9582248263888891</v>
+        <v>0.414333767361111</v>
       </c>
       <c r="C11" t="n">
-        <v>1.638237847222223</v>
+        <v>1.564832899305556</v>
       </c>
       <c r="D11" t="n">
-        <v>8.972185280492686</v>
+        <v>6.865371231208214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5811089409722218</v>
+        <v>0.02365451388888883</v>
       </c>
       <c r="C12" t="n">
-        <v>1.344455295138889</v>
+        <v>1.4091796875</v>
       </c>
       <c r="D12" t="n">
-        <v>3.522775437508385</v>
+        <v>7.398626001704557</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>sporulation__MP_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1038953993055554</v>
+        <v>-0.06727430555555558</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9125976562499999</v>
+        <v>1.236870659722222</v>
       </c>
       <c r="D13" t="n">
-        <v>3.415494297305304</v>
+        <v>4.525521436275775</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incubation__spl_end</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3748372395833333</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.00689019097222</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.231765838264802</v>
       </c>
     </row>
   </sheetData>
